--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="14">
   <si>
     <t>Id</t>
   </si>
@@ -44,7 +44,7 @@
     <t>■</t>
   </si>
   <si>
-    <t>Tr:D3</t>
+    <t>Ar:D4</t>
   </si>
   <si>
     <t>Dr</t>
@@ -64,10 +64,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -85,16 +85,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -108,7 +107,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -117,28 +116,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -160,22 +137,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -189,11 +151,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -213,9 +183,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,7 +238,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -250,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -268,7 +292,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -280,61 +406,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,78 +422,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -432,22 +432,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -467,17 +462,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -515,6 +504,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -537,16 +537,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -558,124 +558,124 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1666,7 +1666,9 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
@@ -1734,7 +1736,7 @@
         <v>8</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>8</v>
@@ -1798,7 +1800,9 @@
         <v>11</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1808,7 +1812,9 @@
       <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
         <v>11</v>

--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -50,6 +50,9 @@
     <t>Dr</t>
   </si>
   <si>
+    <t>Mg</t>
+  </si>
+  <si>
     <t>Ev</t>
   </si>
   <si>
@@ -64,10 +67,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -86,44 +89,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,6 +134,43 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -144,7 +178,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -160,26 +194,26 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -192,38 +226,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,19 +241,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -262,37 +367,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,97 +397,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,12 +425,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -432,17 +435,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -458,15 +479,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -489,17 +501,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,21 +532,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -537,145 +540,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1797,7 +1800,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
@@ -1807,7 +1810,7 @@
         <v>8</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>8</v>
@@ -1817,7 +1820,7 @@
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>8</v>
@@ -1947,7 +1950,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -2511,7 +2514,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>

--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -68,9 +68,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -97,25 +97,31 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -126,8 +132,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -140,14 +155,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -155,8 +162,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -171,9 +179,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -185,40 +201,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,6 +220,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +241,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -253,19 +289,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -277,13 +325,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -301,25 +385,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -331,97 +415,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,35 +435,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -479,6 +461,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -501,23 +492,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -540,145 +540,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1596,15 +1596,11 @@
       <c r="G7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1668,11 +1664,15 @@
         <v>8</v>
       </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
         <v>8</v>
@@ -1733,7 +1733,9 @@
       <c r="F9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
         <v>8</v>
@@ -1745,7 +1747,9 @@
         <v>8</v>
       </c>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="N9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1803,9 +1807,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1815,9 +1817,7 @@
       <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
         <v>12</v>
@@ -1875,7 +1875,9 @@
       <c r="F11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
         <v>8</v>
@@ -1887,7 +1889,9 @@
         <v>8</v>
       </c>
       <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="N11" s="1" t="s">
         <v>8</v>
       </c>
@@ -2019,9 +2023,13 @@
       <c r="H13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="L13" s="1" t="s">
         <v>8</v>
       </c>
@@ -2375,12 +2383,24 @@
       <c r="C18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
         <v>8</v>
@@ -2438,7 +2458,9 @@
       <c r="C19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
@@ -2454,9 +2476,7 @@
       <c r="I19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
         <v>8</v>
       </c>
@@ -2514,25 +2534,25 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>8</v>

--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>InitDir</t>
+  </si>
+  <si>
+    <t>□</t>
   </si>
   <si>
     <t>■</t>
@@ -68,8 +71,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -88,8 +91,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -97,7 +108,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -112,39 +131,63 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -162,24 +205,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -193,40 +221,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +244,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -253,7 +256,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,97 +400,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,61 +418,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,30 +454,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -491,8 +470,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -502,7 +483,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -524,11 +520,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -540,7 +543,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -549,7 +552,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -558,127 +561,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1219,13 +1222,13 @@
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>8</v>
@@ -1296,13 +1299,13 @@
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>8</v>
@@ -1373,11 +1376,11 @@
         <v>8</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>8</v>
@@ -1448,13 +1451,13 @@
         <v>8</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>8</v>
@@ -1519,23 +1522,23 @@
         <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>8</v>
@@ -1594,7 +1597,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1602,7 +1605,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>8</v>
@@ -1661,21 +1664,21 @@
         <v>8</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>8</v>
@@ -1728,33 +1731,33 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>8</v>
@@ -1801,29 +1804,29 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>8</v>
@@ -1870,33 +1873,33 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>8</v>
@@ -1949,17 +1952,17 @@
         <v>8</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>8</v>
@@ -2018,23 +2021,23 @@
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>8</v>
@@ -2099,11 +2102,11 @@
         <v>8</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>8</v>
@@ -2174,11 +2177,11 @@
         <v>8</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>8</v>
@@ -2249,11 +2252,11 @@
         <v>8</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>8</v>
@@ -2324,11 +2327,11 @@
         <v>8</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>8</v>
@@ -2399,11 +2402,11 @@
         <v>8</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>8</v>
@@ -2474,11 +2477,11 @@
         <v>8</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>8</v>
@@ -2549,13 +2552,13 @@
         <v>8</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>8</v>
@@ -2626,13 +2629,13 @@
         <v>8</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>8</v>

--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -56,10 +56,13 @@
     <t>Mg</t>
   </si>
   <si>
-    <t>Ev</t>
+    <t>Ba</t>
   </si>
   <si>
     <t>Un</t>
+  </si>
+  <si>
+    <t>Ev</t>
   </si>
   <si>
     <t>Mv</t>
@@ -72,8 +75,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -91,9 +94,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -107,10 +118,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -119,14 +130,6 @@
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -153,24 +156,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,9 +187,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -206,15 +208,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -222,14 +216,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,7 +253,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -262,13 +367,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -280,7 +397,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -298,133 +421,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,6 +438,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -449,32 +461,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -503,6 +489,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -517,24 +538,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -543,145 +546,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1957,7 +1960,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -2555,7 +2558,7 @@
         <v>9</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>9</v>

--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
     <sheet name="B1F" sheetId="1" r:id="rId2"/>
+    <sheet name="B1F (2)" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -73,9 +74,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -94,45 +95,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -148,8 +110,107 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -163,76 +224,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,7 +248,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -259,7 +284,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -271,13 +380,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,115 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,25 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -445,7 +446,46 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -465,26 +505,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -499,45 +539,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -546,145 +547,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3476,4 +3477,2375 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AO41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="3.27272727272727" customWidth="1"/>
+    <col min="2" max="2" width="2.27272727272727" customWidth="1"/>
+    <col min="3" max="3" width="3.54545454545455" customWidth="1"/>
+    <col min="4" max="8" width="2.27272727272727" customWidth="1"/>
+    <col min="9" max="10" width="3.54545454545455" customWidth="1"/>
+    <col min="11" max="40" width="3.27272727272727" customWidth="1"/>
+    <col min="41" max="41" width="2.81818181818182" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25">
+      <c r="A1" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>16</v>
+      </c>
+      <c r="R1">
+        <v>17</v>
+      </c>
+      <c r="S1">
+        <v>18</v>
+      </c>
+      <c r="T1">
+        <v>19</v>
+      </c>
+      <c r="U1">
+        <v>20</v>
+      </c>
+      <c r="V1">
+        <v>21</v>
+      </c>
+      <c r="W1">
+        <v>22</v>
+      </c>
+      <c r="X1">
+        <v>23</v>
+      </c>
+      <c r="Y1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+    </row>
+    <row r="3" spans="1:41">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+    </row>
+    <row r="4" spans="1:41">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="1"/>
+      <c r="AO4" s="1"/>
+    </row>
+    <row r="5" spans="1:41">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="1"/>
+      <c r="AO5" s="1"/>
+    </row>
+    <row r="6" spans="1:41">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+    </row>
+    <row r="7" spans="1:41">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+    </row>
+    <row r="8" spans="1:41">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="1"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="1"/>
+      <c r="AO8" s="1"/>
+    </row>
+    <row r="9" spans="1:41">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="1"/>
+      <c r="AO9" s="1"/>
+    </row>
+    <row r="10" spans="1:41">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="1"/>
+      <c r="AI10" s="1"/>
+      <c r="AJ10" s="1"/>
+      <c r="AK10" s="1"/>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="1"/>
+      <c r="AO10" s="1"/>
+    </row>
+    <row r="11" spans="1:41">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+      <c r="AL11" s="1"/>
+      <c r="AM11" s="1"/>
+      <c r="AN11" s="1"/>
+      <c r="AO11" s="1"/>
+    </row>
+    <row r="12" spans="1:41">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="1"/>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="1"/>
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="1"/>
+      <c r="AO12" s="1"/>
+    </row>
+    <row r="13" spans="1:41">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="1"/>
+      <c r="AI13" s="1"/>
+      <c r="AJ13" s="1"/>
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
+      <c r="AM13" s="1"/>
+      <c r="AN13" s="1"/>
+      <c r="AO13" s="1"/>
+    </row>
+    <row r="14" spans="1:41">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
+      <c r="AI14" s="1"/>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="1"/>
+    </row>
+    <row r="15" spans="1:41">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1"/>
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="1"/>
+      <c r="AO15" s="1"/>
+    </row>
+    <row r="16" spans="1:41">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+      <c r="AI16" s="1"/>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1"/>
+      <c r="AL16" s="1"/>
+      <c r="AM16" s="1"/>
+      <c r="AN16" s="1"/>
+      <c r="AO16" s="1"/>
+    </row>
+    <row r="17" spans="1:41">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+      <c r="AI17" s="1"/>
+      <c r="AJ17" s="1"/>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="1"/>
+      <c r="AO17" s="1"/>
+    </row>
+    <row r="18" spans="1:41">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1"/>
+      <c r="AJ18" s="1"/>
+      <c r="AK18" s="1"/>
+      <c r="AL18" s="1"/>
+      <c r="AM18" s="1"/>
+      <c r="AN18" s="1"/>
+      <c r="AO18" s="1"/>
+    </row>
+    <row r="19" spans="1:41">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+      <c r="AJ19" s="1"/>
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="1"/>
+    </row>
+    <row r="20" spans="1:41">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1"/>
+    </row>
+    <row r="21" spans="1:41">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+      <c r="AI21" s="1"/>
+      <c r="AJ21" s="1"/>
+      <c r="AK21" s="1"/>
+      <c r="AL21" s="1"/>
+      <c r="AM21" s="1"/>
+      <c r="AN21" s="1"/>
+      <c r="AO21" s="1"/>
+    </row>
+    <row r="22" spans="1:41">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1"/>
+      <c r="AG22" s="1"/>
+      <c r="AH22" s="1"/>
+      <c r="AI22" s="1"/>
+      <c r="AJ22" s="1"/>
+      <c r="AK22" s="1"/>
+      <c r="AL22" s="1"/>
+      <c r="AM22" s="1"/>
+      <c r="AN22" s="1"/>
+      <c r="AO22" s="1"/>
+    </row>
+    <row r="23" spans="1:41">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1"/>
+      <c r="AG23" s="1"/>
+      <c r="AH23" s="1"/>
+      <c r="AI23" s="1"/>
+      <c r="AJ23" s="1"/>
+      <c r="AK23" s="1"/>
+      <c r="AL23" s="1"/>
+      <c r="AM23" s="1"/>
+      <c r="AN23" s="1"/>
+      <c r="AO23" s="1"/>
+    </row>
+    <row r="24" spans="1:41">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="1"/>
+      <c r="AO24" s="1"/>
+    </row>
+    <row r="25" spans="1:41">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="1"/>
+      <c r="AI25" s="1"/>
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="1"/>
+      <c r="AL25" s="1"/>
+      <c r="AM25" s="1"/>
+      <c r="AN25" s="1"/>
+      <c r="AO25" s="1"/>
+    </row>
+    <row r="26" spans="2:41">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+      <c r="AO26" s="1"/>
+    </row>
+    <row r="27" spans="2:41">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
+      <c r="AI27" s="1"/>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1"/>
+      <c r="AL27" s="1"/>
+      <c r="AM27" s="1"/>
+      <c r="AN27" s="1"/>
+      <c r="AO27" s="1"/>
+    </row>
+    <row r="28" spans="2:41">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
+      <c r="AI28" s="1"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1"/>
+      <c r="AL28" s="1"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="1"/>
+      <c r="AO28" s="1"/>
+    </row>
+    <row r="29" spans="2:41">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="1"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1"/>
+      <c r="AO29" s="1"/>
+    </row>
+    <row r="30" spans="2:41">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+      <c r="AG30" s="1"/>
+      <c r="AH30" s="1"/>
+      <c r="AI30" s="1"/>
+      <c r="AJ30" s="1"/>
+      <c r="AK30" s="1"/>
+      <c r="AL30" s="1"/>
+      <c r="AM30" s="1"/>
+      <c r="AN30" s="1"/>
+      <c r="AO30" s="1"/>
+    </row>
+    <row r="31" spans="2:41">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1"/>
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="1"/>
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="1"/>
+      <c r="AO31" s="1"/>
+    </row>
+    <row r="32" spans="2:41">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="1"/>
+      <c r="AO32" s="1"/>
+    </row>
+    <row r="33" spans="2:41">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="1"/>
+      <c r="AM33" s="1"/>
+      <c r="AN33" s="1"/>
+      <c r="AO33" s="1"/>
+    </row>
+    <row r="34" spans="2:41">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AI34" s="1"/>
+      <c r="AJ34" s="1"/>
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="1"/>
+      <c r="AM34" s="1"/>
+      <c r="AN34" s="1"/>
+      <c r="AO34" s="1"/>
+    </row>
+    <row r="35" spans="2:41">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+      <c r="AG35" s="1"/>
+      <c r="AH35" s="1"/>
+      <c r="AI35" s="1"/>
+      <c r="AJ35" s="1"/>
+      <c r="AK35" s="1"/>
+      <c r="AL35" s="1"/>
+      <c r="AM35" s="1"/>
+      <c r="AN35" s="1"/>
+      <c r="AO35" s="1"/>
+    </row>
+    <row r="36" spans="2:41">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AH36" s="1"/>
+      <c r="AI36" s="1"/>
+      <c r="AJ36" s="1"/>
+      <c r="AK36" s="1"/>
+      <c r="AL36" s="1"/>
+      <c r="AM36" s="1"/>
+      <c r="AN36" s="1"/>
+      <c r="AO36" s="1"/>
+    </row>
+    <row r="37" spans="2:41">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+      <c r="AG37" s="1"/>
+      <c r="AH37" s="1"/>
+      <c r="AI37" s="1"/>
+      <c r="AJ37" s="1"/>
+      <c r="AK37" s="1"/>
+      <c r="AL37" s="1"/>
+      <c r="AM37" s="1"/>
+      <c r="AN37" s="1"/>
+      <c r="AO37" s="1"/>
+    </row>
+    <row r="38" spans="2:41">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1"/>
+      <c r="AG38" s="1"/>
+      <c r="AH38" s="1"/>
+      <c r="AI38" s="1"/>
+      <c r="AJ38" s="1"/>
+      <c r="AK38" s="1"/>
+      <c r="AL38" s="1"/>
+      <c r="AM38" s="1"/>
+      <c r="AN38" s="1"/>
+      <c r="AO38" s="1"/>
+    </row>
+    <row r="39" spans="2:41">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1"/>
+      <c r="AG39" s="1"/>
+      <c r="AH39" s="1"/>
+      <c r="AI39" s="1"/>
+      <c r="AJ39" s="1"/>
+      <c r="AK39" s="1"/>
+      <c r="AL39" s="1"/>
+      <c r="AM39" s="1"/>
+      <c r="AN39" s="1"/>
+      <c r="AO39" s="1"/>
+    </row>
+    <row r="40" spans="2:41">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1"/>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+      <c r="AG40" s="1"/>
+      <c r="AH40" s="1"/>
+      <c r="AI40" s="1"/>
+      <c r="AJ40" s="1"/>
+      <c r="AK40" s="1"/>
+      <c r="AL40" s="1"/>
+      <c r="AM40" s="1"/>
+      <c r="AN40" s="1"/>
+      <c r="AO40" s="1"/>
+    </row>
+    <row r="41" spans="2:41">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1"/>
+      <c r="AF41" s="1"/>
+      <c r="AG41" s="1"/>
+      <c r="AH41" s="1"/>
+      <c r="AI41" s="1"/>
+      <c r="AJ41" s="1"/>
+      <c r="AK41" s="1"/>
+      <c r="AL41" s="1"/>
+      <c r="AM41" s="1"/>
+      <c r="AN41" s="1"/>
+      <c r="AO41" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -51,16 +51,13 @@
     <t>Ar:D4</t>
   </si>
   <si>
-    <t>Dr</t>
-  </si>
-  <si>
-    <t>Mg</t>
-  </si>
-  <si>
     <t>Ba</t>
   </si>
   <si>
     <t>Un</t>
+  </si>
+  <si>
+    <t>Dr</t>
   </si>
   <si>
     <t>Ev</t>
@@ -95,15 +92,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -117,9 +130,63 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -133,55 +200,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -189,13 +209,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -211,22 +224,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,6 +245,114 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -260,7 +365,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -272,19 +383,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,13 +413,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -314,121 +425,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +443,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -455,7 +452,63 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -475,67 +528,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -547,7 +544,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -556,7 +553,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -565,127 +562,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1226,13 +1223,13 @@
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>8</v>
@@ -1303,13 +1300,13 @@
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>8</v>
@@ -1380,11 +1377,13 @@
         <v>8</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>8</v>
@@ -1455,13 +1454,13 @@
         <v>8</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>8</v>
@@ -1526,23 +1525,25 @@
         <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>8</v>
@@ -1601,15 +1602,25 @@
         <v>8</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="M7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>8</v>
@@ -1668,21 +1679,25 @@
         <v>8</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="I8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="M8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>8</v>
@@ -1743,17 +1758,21 @@
       <c r="G9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="M9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1811,7 +1830,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1819,7 +1838,7 @@
         <v>9</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>9</v>
@@ -1827,7 +1846,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>9</v>
@@ -1890,7 +1909,7 @@
         <v>9</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>9</v>
@@ -1961,7 +1980,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -2559,7 +2578,7 @@
         <v>9</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>9</v>
@@ -3597,13 +3616,13 @@
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>8</v>
@@ -3674,13 +3693,13 @@
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>8</v>
@@ -3751,11 +3770,13 @@
         <v>8</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>8</v>
@@ -3826,13 +3847,13 @@
         <v>8</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>8</v>
@@ -3897,23 +3918,25 @@
         <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>8</v>
@@ -3972,15 +3995,25 @@
         <v>8</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="M7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>8</v>
@@ -4039,21 +4072,25 @@
         <v>8</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="I8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="M8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>8</v>
@@ -4114,17 +4151,21 @@
       <c r="G9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="M9" s="1" t="s">
         <v>9</v>
       </c>
@@ -4182,7 +4223,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -4190,7 +4231,7 @@
         <v>9</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>9</v>
@@ -4198,7 +4239,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>9</v>
@@ -4261,7 +4302,7 @@
         <v>9</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>9</v>
@@ -4332,7 +4373,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -4930,7 +4971,7 @@
         <v>9</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>9</v>

--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -71,10 +71,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -92,6 +92,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -101,7 +145,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,7 +198,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -130,107 +228,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,13 +245,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,7 +287,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,49 +317,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,12 +353,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -353,19 +365,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,55 +395,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,11 +439,46 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -488,32 +523,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -527,15 +536,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -544,145 +544,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -72,8 +72,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -93,14 +93,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -108,15 +116,31 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -136,16 +160,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -160,14 +199,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -176,45 +207,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,9 +221,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,6 +242,36 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -257,55 +287,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,37 +323,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,49 +341,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,6 +359,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -429,6 +423,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -436,6 +436,41 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -454,31 +489,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -507,32 +528,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -544,7 +544,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -553,7 +553,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -562,127 +562,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1084,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>20</v>

--- a/Assets/Data/Dungeon0042.xlsx
+++ b/Assets/Data/Dungeon0042.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -55,13 +55,16 @@
     <t>Ar:D4</t>
   </si>
   <si>
+    <t>Dr</t>
+  </si>
+  <si>
+    <t>Mg</t>
+  </si>
+  <si>
     <t>Ba</t>
   </si>
   <si>
     <t>Un</t>
-  </si>
-  <si>
-    <t>Dr</t>
   </si>
   <si>
     <t>Ev</t>
@@ -102,9 +105,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -131,15 +134,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -160,32 +185,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,6 +217,22 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -208,14 +241,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,39 +262,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,7 +279,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -288,7 +291,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,7 +315,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,13 +357,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -330,133 +459,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,25 +474,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,17 +503,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -529,6 +526,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -558,15 +570,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -575,16 +578,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -596,124 +599,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -829,169 +832,177 @@
         </row>
         <row r="4">
           <cell r="D4">
-            <v>2010</v>
+            <v>1020</v>
           </cell>
           <cell r="E4" t="str">
-            <v>ダンジョンから出る</v>
+            <v>エンフェリアイベント再生</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2021</v>
+            <v>2020</v>
           </cell>
           <cell r="E6" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2030</v>
+            <v>2021</v>
           </cell>
           <cell r="E7" t="str">
-            <v>ダンジョンクリア</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3010</v>
+            <v>2030</v>
           </cell>
           <cell r="E8" t="str">
-            <v>アーティファクト取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3020</v>
+            <v>3010</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アイテム取得</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3030</v>
+            <v>3020</v>
           </cell>
           <cell r="E10" t="str">
-            <v>魔法入手</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>4010</v>
+            <v>3030</v>
           </cell>
           <cell r="E11" t="str">
-            <v>仲間を増やす</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4011</v>
+            <v>4010</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を外す</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4020</v>
+            <v>4011</v>
           </cell>
           <cell r="E13" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>5010</v>
+            <v>4020</v>
           </cell>
           <cell r="E14" t="str">
-            <v>強制戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5020</v>
+            <v>5010</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制ボス戦闘</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>6010</v>
+            <v>5020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6011</v>
+            <v>6010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6020</v>
+            <v>6011</v>
           </cell>
           <cell r="E18" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6030</v>
+            <v>6020</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>7010</v>
+            <v>6030</v>
           </cell>
           <cell r="E20" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7020</v>
+            <v>7010</v>
           </cell>
           <cell r="E21" t="str">
-            <v>怨嗟床</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7021</v>
+            <v>7020</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床解除</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>8010</v>
+            <v>7021</v>
           </cell>
           <cell r="E23" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床解除</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
+            <v>8010</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
             <v>9010</v>
           </cell>
-          <cell r="E24" t="str">
+          <cell r="E25" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -1621,13 +1632,13 @@
         <v>8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>8</v>
@@ -1698,13 +1709,13 @@
         <v>8</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>8</v>
@@ -1775,13 +1786,13 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>8</v>
@@ -1852,13 +1863,11 @@
         <v>8</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
@@ -1932,7 +1941,7 @@
         <v>9</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>9</v>
@@ -2008,9 +2017,7 @@
       <c r="I9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
         <v>9</v>
       </c>
@@ -2074,7 +2081,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2082,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>9</v>
@@ -2090,7 +2097,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>9</v>
@@ -2153,7 +2160,7 @@
         <v>9</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>9</v>
@@ -2224,7 +2231,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -2822,7 +2829,7 @@
         <v>9</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>9</v>
@@ -4014,13 +4021,13 @@
         <v>8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>8</v>
@@ -4091,13 +4098,13 @@
         <v>8</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>8</v>
@@ -4168,13 +4175,11 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>8</v>
@@ -4245,13 +4250,11 @@
         <v>8</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
@@ -4324,9 +4327,7 @@
       <c r="I8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
         <v>9</v>
       </c>
@@ -4401,9 +4402,7 @@
       <c r="I9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
         <v>9</v>
       </c>
@@ -4467,7 +4466,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -4475,7 +4474,7 @@
         <v>9</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>9</v>
@@ -4483,7 +4482,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>9</v>
@@ -4546,7 +4545,7 @@
         <v>9</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>9</v>
@@ -4617,7 +4616,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -5215,7 +5214,7 @@
         <v>9</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>9</v>
@@ -6138,42 +6137,45 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <cols>
+    <col min="7" max="7" width="39.8181818181818" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -6217,7 +6219,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>3010</v>
@@ -6338,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -6598,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -6693,7 +6695,168 @@
         <v>0</v>
       </c>
       <c r="K17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>42</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>3010</v>
+      </c>
+      <c r="F18">
+        <v>1010</v>
+      </c>
+      <c r="G18" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F18,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H18">
+        <v>140</v>
+      </c>
+      <c r="I18">
         <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>42</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>3010</v>
+      </c>
+      <c r="F19">
+        <v>6010</v>
+      </c>
+      <c r="G19" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F19,[1]Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H19">
+        <v>86</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>42</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>3010</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>86</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>42</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>3010</v>
+      </c>
+      <c r="F21">
+        <v>1020</v>
+      </c>
+      <c r="G21" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F21,[1]Define!D:D))</f>
+        <v>エンフェリアイベント再生</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22">
+        <v>42</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>3010</v>
+      </c>
+      <c r="F22">
+        <v>9010</v>
+      </c>
+      <c r="G22" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F22,[1]Define!D:D))</f>
+        <v>イベント終了明示</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
